--- a/excel/test_endurance.xlsx
+++ b/excel/test_endurance.xlsx
@@ -425,7 +425,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>69.11830139160156</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="3">
@@ -440,7 +440,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>75.50160217285156</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="6">
@@ -495,7 +495,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>67.95210266113281</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="17">
@@ -530,7 +530,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>72.01980590820312</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="24">
@@ -575,7 +575,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>74.34101104736328</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="33">
@@ -615,7 +615,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>68.53604125976562</v>
+        <v>67.3681640625</v>
       </c>
     </row>
     <row r="41">
@@ -660,7 +660,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>76.0819091796875</v>
+        <v>67.3681640625</v>
       </c>
     </row>
   </sheetData>
